--- a/public/templates/IES-Project-Template-v3.xlsx
+++ b/public/templates/IES-Project-Template-v3.xlsx
@@ -695,7 +695,7 @@
     <t>Template version</t>
   </si>
   <si>
-    <t>v2 (Sprint 8B) — Project doc-default columns, Buildings engineer + arabic_name, and the Items sheet.</t>
+    <t>v3 (Sprint 8C) — colour-coded header sections, standalone-COC default + coc_bundle_key, Building Info columns (type / electrical / responsible person / operating hours), and pm_name/engineer_name display overrides.</t>
   </si>
   <si>
     <t>Section swatches</t>

--- a/public/templates/IES-Project-Template-v3.xlsx
+++ b/public/templates/IES-Project-Template-v3.xlsx
@@ -206,13 +206,6 @@
     <comment ref="AA1" authorId="0">
       <text>
         <r>
-          <t>Optional · defaults section</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AB1" authorId="0">
-      <text>
-        <r>
           <t>Optional · id section</t>
         </r>
       </text>
@@ -570,7 +563,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="164">
   <si>
     <t>IES — Project Import Template</t>
   </si>
@@ -797,9 +790,6 @@
     <t>subcontractor</t>
   </si>
   <si>
-    <t>coc_layout</t>
-  </si>
-  <si>
     <t>coc_bundle_key</t>
   </si>
   <si>
@@ -860,9 +850,6 @@
     <t>Tarshid</t>
   </si>
   <si>
-    <t>concatenated</t>
-  </si>
-  <si>
     <t>DELETE-BEFORE-UPLOAD</t>
   </si>
   <si>
@@ -1031,13 +1018,7 @@
     <t>LED 40W Ceiling Panel</t>
   </si>
   <si>
-    <t>Philips</t>
-  </si>
-  <si>
     <t>Split WM 1.5 TR</t>
-  </si>
-  <si>
-    <t>Trane</t>
   </si>
   <si>
     <t>old_code</t>
@@ -1864,7 +1845,7 @@
   <sheetPr>
     <tabColor rgb="FF2563EB"/>
   </sheetPr>
-  <dimension ref="A1:AB25"/>
+  <dimension ref="A1:AA25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -1886,11 +1867,11 @@
     <col min="22" max="23" width="16" customWidth="1"/>
     <col min="24" max="24" width="22" customWidth="1"/>
     <col min="25" max="25" width="20" customWidth="1"/>
-    <col min="26" max="27" width="16" customWidth="1"/>
-    <col min="28" max="28" width="22" customWidth="1"/>
+    <col min="26" max="26" width="16" customWidth="1"/>
+    <col min="27" max="27" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" ht="24" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>50</v>
       </c>
@@ -1969,43 +1950,40 @@
       <c r="Z1" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="AA1" s="22" t="s">
+      <c r="AA1" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="AB1" s="16" t="s">
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A2" s="23" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
+      <c r="B2" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="C2" s="23" t="s">
         <v>79</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="D2" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="E2" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="F2" s="23" t="s">
         <v>82</v>
-      </c>
-      <c r="F2" s="23" t="s">
-        <v>83</v>
       </c>
       <c r="G2" s="23">
         <v>64</v>
       </c>
       <c r="H2" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="I2" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="I2" s="23" t="s">
+      <c r="J2" s="23" t="s">
         <v>85</v>
-      </c>
-      <c r="J2" s="23" t="s">
-        <v>86</v>
       </c>
       <c r="K2" s="23" t="s">
         <v>1</v>
@@ -2014,16 +1992,16 @@
         <v>1</v>
       </c>
       <c r="M2" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="N2" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="N2" s="23" t="s">
+      <c r="O2" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="O2" s="23" t="s">
+      <c r="P2" s="23" t="s">
         <v>89</v>
-      </c>
-      <c r="P2" s="23" t="s">
-        <v>90</v>
       </c>
       <c r="Q2" s="24">
         <v>18.2164</v>
@@ -2032,37 +2010,34 @@
         <v>42.5053</v>
       </c>
       <c r="S2" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="T2" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="U2" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="T2" s="23" t="s">
-        <v>80</v>
-      </c>
-      <c r="U2" s="23" t="s">
+      <c r="V2" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="V2" s="23" t="s">
+      <c r="W2" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="W2" s="23" t="s">
+      <c r="X2" s="23" t="s">
         <v>94</v>
-      </c>
-      <c r="X2" s="23" t="s">
-        <v>95</v>
       </c>
       <c r="Y2" s="23" t="s">
         <v>1</v>
       </c>
       <c r="Z2" s="23" t="s">
-        <v>96</v>
+        <v>1</v>
       </c>
       <c r="AA2" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB2" s="23" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="25"/>
       <c r="B3" s="25"/>
       <c r="C3" s="26"/>
@@ -2090,9 +2065,8 @@
       <c r="Y3" s="26"/>
       <c r="Z3" s="26"/>
       <c r="AA3" s="26"/>
-      <c r="AB3" s="26"/>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="25"/>
       <c r="C4" s="26"/>
@@ -2120,9 +2094,8 @@
       <c r="Y4" s="26"/>
       <c r="Z4" s="26"/>
       <c r="AA4" s="26"/>
-      <c r="AB4" s="26"/>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="25"/>
       <c r="B5" s="25"/>
       <c r="C5" s="26"/>
@@ -2150,9 +2123,8 @@
       <c r="Y5" s="26"/>
       <c r="Z5" s="26"/>
       <c r="AA5" s="26"/>
-      <c r="AB5" s="26"/>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="25"/>
       <c r="B6" s="25"/>
       <c r="C6" s="26"/>
@@ -2180,9 +2152,8 @@
       <c r="Y6" s="26"/>
       <c r="Z6" s="26"/>
       <c r="AA6" s="26"/>
-      <c r="AB6" s="26"/>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="25"/>
       <c r="B7" s="25"/>
       <c r="C7" s="26"/>
@@ -2210,9 +2181,8 @@
       <c r="Y7" s="26"/>
       <c r="Z7" s="26"/>
       <c r="AA7" s="26"/>
-      <c r="AB7" s="26"/>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="25"/>
       <c r="B8" s="25"/>
       <c r="C8" s="26"/>
@@ -2240,9 +2210,8 @@
       <c r="Y8" s="26"/>
       <c r="Z8" s="26"/>
       <c r="AA8" s="26"/>
-      <c r="AB8" s="26"/>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="25"/>
       <c r="B9" s="25"/>
       <c r="C9" s="26"/>
@@ -2270,9 +2239,8 @@
       <c r="Y9" s="26"/>
       <c r="Z9" s="26"/>
       <c r="AA9" s="26"/>
-      <c r="AB9" s="26"/>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="25"/>
       <c r="B10" s="25"/>
       <c r="C10" s="26"/>
@@ -2300,9 +2268,8 @@
       <c r="Y10" s="26"/>
       <c r="Z10" s="26"/>
       <c r="AA10" s="26"/>
-      <c r="AB10" s="26"/>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="25"/>
       <c r="B11" s="25"/>
       <c r="C11" s="26"/>
@@ -2330,9 +2297,8 @@
       <c r="Y11" s="26"/>
       <c r="Z11" s="26"/>
       <c r="AA11" s="26"/>
-      <c r="AB11" s="26"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="25"/>
       <c r="B12" s="25"/>
       <c r="C12" s="26"/>
@@ -2360,9 +2326,8 @@
       <c r="Y12" s="26"/>
       <c r="Z12" s="26"/>
       <c r="AA12" s="26"/>
-      <c r="AB12" s="26"/>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="25"/>
       <c r="B13" s="25"/>
       <c r="C13" s="26"/>
@@ -2390,9 +2355,8 @@
       <c r="Y13" s="26"/>
       <c r="Z13" s="26"/>
       <c r="AA13" s="26"/>
-      <c r="AB13" s="26"/>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="25"/>
       <c r="B14" s="25"/>
       <c r="C14" s="26"/>
@@ -2420,9 +2384,8 @@
       <c r="Y14" s="26"/>
       <c r="Z14" s="26"/>
       <c r="AA14" s="26"/>
-      <c r="AB14" s="26"/>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="25"/>
       <c r="B15" s="25"/>
       <c r="C15" s="26"/>
@@ -2450,9 +2413,8 @@
       <c r="Y15" s="26"/>
       <c r="Z15" s="26"/>
       <c r="AA15" s="26"/>
-      <c r="AB15" s="26"/>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="25"/>
       <c r="B16" s="25"/>
       <c r="C16" s="26"/>
@@ -2480,9 +2442,8 @@
       <c r="Y16" s="26"/>
       <c r="Z16" s="26"/>
       <c r="AA16" s="26"/>
-      <c r="AB16" s="26"/>
-    </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A17" s="25"/>
       <c r="B17" s="25"/>
       <c r="C17" s="26"/>
@@ -2510,9 +2471,8 @@
       <c r="Y17" s="26"/>
       <c r="Z17" s="26"/>
       <c r="AA17" s="26"/>
-      <c r="AB17" s="26"/>
-    </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" s="25"/>
       <c r="B18" s="25"/>
       <c r="C18" s="26"/>
@@ -2540,9 +2500,8 @@
       <c r="Y18" s="26"/>
       <c r="Z18" s="26"/>
       <c r="AA18" s="26"/>
-      <c r="AB18" s="26"/>
-    </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" s="25"/>
       <c r="B19" s="25"/>
       <c r="C19" s="26"/>
@@ -2570,9 +2529,8 @@
       <c r="Y19" s="26"/>
       <c r="Z19" s="26"/>
       <c r="AA19" s="26"/>
-      <c r="AB19" s="26"/>
-    </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" s="25"/>
       <c r="B20" s="25"/>
       <c r="C20" s="26"/>
@@ -2600,9 +2558,8 @@
       <c r="Y20" s="26"/>
       <c r="Z20" s="26"/>
       <c r="AA20" s="26"/>
-      <c r="AB20" s="26"/>
-    </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A21" s="25"/>
       <c r="B21" s="25"/>
       <c r="C21" s="26"/>
@@ -2630,9 +2587,8 @@
       <c r="Y21" s="26"/>
       <c r="Z21" s="26"/>
       <c r="AA21" s="26"/>
-      <c r="AB21" s="26"/>
-    </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A22" s="25"/>
       <c r="B22" s="25"/>
       <c r="C22" s="26"/>
@@ -2660,9 +2616,8 @@
       <c r="Y22" s="26"/>
       <c r="Z22" s="26"/>
       <c r="AA22" s="26"/>
-      <c r="AB22" s="26"/>
-    </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A23" s="25"/>
       <c r="B23" s="25"/>
       <c r="C23" s="26"/>
@@ -2690,9 +2645,8 @@
       <c r="Y23" s="26"/>
       <c r="Z23" s="26"/>
       <c r="AA23" s="26"/>
-      <c r="AB23" s="26"/>
-    </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A24" s="25"/>
       <c r="B24" s="25"/>
       <c r="C24" s="26"/>
@@ -2720,9 +2674,8 @@
       <c r="Y24" s="26"/>
       <c r="Z24" s="26"/>
       <c r="AA24" s="26"/>
-      <c r="AB24" s="26"/>
-    </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A25" s="25"/>
       <c r="B25" s="25"/>
       <c r="C25" s="26"/>
@@ -2750,21 +2703,14 @@
       <c r="Y25" s="26"/>
       <c r="Z25" s="26"/>
       <c r="AA25" s="26"/>
-      <c r="AB25" s="26"/>
     </row>
   </sheetData>
-  <dataValidations count="4">
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" error="Pick one of: active, draft, on_hold, closed" sqref="H10:H25">
       <formula1>"active,draft,on_hold,closed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" error="Pick one of: active, draft, on_hold, closed" sqref="H2:H25">
       <formula1>"active,draft,on_hold,closed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" error="Pick one of: concatenated, scattered" sqref="Z10:Z25">
-      <formula1>"concatenated,scattered"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" error="Pick one of: concatenated, scattered" sqref="Z2:Z25">
-      <formula1>"concatenated,scattered"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2804,16 +2750,16 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="D1" s="20" t="s">
         <v>99</v>
-      </c>
-      <c r="C1" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="D1" s="20" t="s">
-        <v>101</v>
       </c>
       <c r="E1" s="21" t="s">
         <v>66</v>
@@ -2822,10 +2768,10 @@
         <v>67</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I1" s="19" t="s">
         <v>62</v>
@@ -2837,48 +2783,48 @@
         <v>57</v>
       </c>
       <c r="L1" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M1" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="N1" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="O1" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="N1" s="16" t="s">
+      <c r="P1" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="O1" s="27" t="s">
+      <c r="Q1" s="27" t="s">
         <v>106</v>
       </c>
-      <c r="P1" s="27" t="s">
+      <c r="R1" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="Q1" s="27" t="s">
+      <c r="S1" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="R1" s="27" t="s">
+      <c r="T1" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="S1" s="19" t="s">
+      <c r="U1" s="17" t="s">
         <v>110</v>
-      </c>
-      <c r="T1" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="U1" s="17" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B2" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="D2" s="23" t="s">
         <v>113</v>
-      </c>
-      <c r="C2" s="23" t="s">
-        <v>114</v>
-      </c>
-      <c r="D2" s="23" t="s">
-        <v>115</v>
       </c>
       <c r="E2" s="24">
         <v>18.2164</v>
@@ -2893,40 +2839,40 @@
         <v>4200</v>
       </c>
       <c r="I2" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="J2" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="J2" s="23" t="s">
-        <v>88</v>
-      </c>
       <c r="K2" s="23" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L2" s="23" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="M2" s="23" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N2" s="23" t="s">
         <v>1</v>
       </c>
       <c r="O2" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="P2" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q2" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="P2" s="23" t="s">
+      <c r="R2" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="Q2" s="23" t="s">
+      <c r="S2" s="23" t="s">
         <v>119</v>
       </c>
-      <c r="R2" s="23" t="s">
+      <c r="T2" s="23" t="s">
         <v>120</v>
-      </c>
-      <c r="S2" s="23" t="s">
-        <v>121</v>
-      </c>
-      <c r="T2" s="23" t="s">
-        <v>122</v>
       </c>
       <c r="U2" s="23">
         <v>3120</v>
@@ -2934,16 +2880,16 @@
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B3" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" s="23" t="s">
         <v>123</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>124</v>
-      </c>
-      <c r="D3" s="23" t="s">
-        <v>125</v>
       </c>
       <c r="E3" s="24">
         <v>18.3</v>
@@ -2958,40 +2904,40 @@
         <v>2600</v>
       </c>
       <c r="I3" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="J3" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="K3" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="J3" s="23" t="s">
-        <v>127</v>
-      </c>
-      <c r="K3" s="23" t="s">
-        <v>128</v>
-      </c>
       <c r="L3" s="23" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="M3" s="23" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N3" s="23" t="s">
         <v>1</v>
       </c>
       <c r="O3" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="P3" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q3" s="23" t="s">
         <v>129</v>
       </c>
-      <c r="P3" s="23" t="s">
+      <c r="R3" s="23" t="s">
         <v>130</v>
       </c>
-      <c r="Q3" s="23" t="s">
+      <c r="S3" s="23" t="s">
         <v>131</v>
       </c>
-      <c r="R3" s="23" t="s">
+      <c r="T3" s="23" t="s">
         <v>132</v>
-      </c>
-      <c r="S3" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="T3" s="23" t="s">
-        <v>134</v>
       </c>
       <c r="U3" s="23">
         <v>3120</v>
@@ -3535,71 +3481,71 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B1" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="D1" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="E1" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="F1" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="G1" s="16" t="s">
         <v>138</v>
-      </c>
-      <c r="F1" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="G1" s="16" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B2" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="D2" s="23" t="s">
         <v>141</v>
-      </c>
-      <c r="C2" s="23" t="s">
-        <v>142</v>
-      </c>
-      <c r="D2" s="23" t="s">
-        <v>143</v>
       </c>
       <c r="E2" s="23">
         <v>120</v>
       </c>
       <c r="F2" s="23" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G2" s="23" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B3" s="23" t="s">
+        <v>143</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="D3" s="23" t="s">
         <v>145</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="D3" s="23" t="s">
-        <v>147</v>
       </c>
       <c r="E3" s="23">
         <v>15</v>
       </c>
       <c r="F3" s="23" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G3" s="23" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -3832,62 +3778,62 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B1" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="F1" s="16" t="s">
         <v>149</v>
-      </c>
-      <c r="C1" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="D1" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="E1" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="F1" s="16" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="D2" s="23" t="s">
         <v>142</v>
-      </c>
-      <c r="B2" s="23" t="s">
-        <v>152</v>
-      </c>
-      <c r="C2" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="D2" s="23" t="s">
-        <v>144</v>
       </c>
       <c r="E2" s="23">
         <v>1000</v>
       </c>
       <c r="F2" s="23" t="s">
-        <v>153</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>143</v>
+      </c>
+      <c r="D3" s="23" t="s">
         <v>146</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>154</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>145</v>
-      </c>
-      <c r="D3" s="23" t="s">
-        <v>148</v>
       </c>
       <c r="E3" s="23">
         <v>200</v>
       </c>
       <c r="F3" s="23" t="s">
-        <v>155</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -4103,98 +4049,98 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C1" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="G1" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="H1" s="16" t="s">
         <v>157</v>
       </c>
-      <c r="E1" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="F1" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="G1" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="H1" s="16" t="s">
-        <v>161</v>
-      </c>
       <c r="I1" s="16" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="J1" s="16" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E2" s="23">
         <v>4</v>
       </c>
       <c r="F2" s="23" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G2" s="23" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="H2" s="23">
         <v>4</v>
       </c>
       <c r="I2" s="23" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J2" s="23" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E3" s="23">
         <v>120</v>
       </c>
       <c r="F3" s="23" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G3" s="23" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="H3" s="23">
         <v>120</v>
       </c>
       <c r="I3" s="23" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J3" s="23" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">

--- a/public/templates/IES-Project-Template-v3.xlsx
+++ b/public/templates/IES-Project-Template-v3.xlsx
@@ -563,7 +563,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="158">
   <si>
     <t>IES — Project Import Template</t>
   </si>
@@ -796,16 +796,16 @@
     <t>remarks</t>
   </si>
   <si>
-    <t>MOI-ASIR</t>
-  </si>
-  <si>
-    <t>MOI — Asir Region</t>
-  </si>
-  <si>
-    <t>Ministry of Interior</t>
-  </si>
-  <si>
-    <t>Asir</t>
+    <t>PRJ-001</t>
+  </si>
+  <si>
+    <t>Sample Project</t>
+  </si>
+  <si>
+    <t>Sample Client Entity</t>
+  </si>
+  <si>
+    <t>Sample Region</t>
   </si>
   <si>
     <t>2025-09-01</t>
@@ -817,25 +817,25 @@
     <t>active</t>
   </si>
   <si>
-    <t>majed.alqahtani@ies.demo.local</t>
-  </si>
-  <si>
-    <t>yousef.almaliki@ies.demo.local</t>
-  </si>
-  <si>
-    <t>Al-Faisal HVAC</t>
-  </si>
-  <si>
-    <t>+966 50 000 0000</t>
-  </si>
-  <si>
-    <t>ops@alfaisal.example</t>
-  </si>
-  <si>
-    <t>Abha, Asir</t>
-  </si>
-  <si>
-    <t>MOI-ASIR-2025</t>
+    <t>pm@example.com</t>
+  </si>
+  <si>
+    <t>engineer@example.com</t>
+  </si>
+  <si>
+    <t>Contractor name</t>
+  </si>
+  <si>
+    <t>+000 000 0000</t>
+  </si>
+  <si>
+    <t>contractor@example.com</t>
+  </si>
+  <si>
+    <t>Sample City, Sample Region</t>
+  </si>
+  <si>
+    <t>REF-0001</t>
   </si>
   <si>
     <t>00</t>
@@ -847,7 +847,7 @@
     <t>2027-01-15</t>
   </si>
   <si>
-    <t>Tarshid</t>
+    <t>ESCO name</t>
   </si>
   <si>
     <t>DELETE-BEFORE-UPLOAD</t>
@@ -898,70 +898,52 @@
     <t>operating_hours</t>
   </si>
   <si>
-    <t>MOI-001</t>
-  </si>
-  <si>
-    <t>Police HQ — Abha</t>
-  </si>
-  <si>
-    <t>Abha</t>
+    <t>BLD-001</t>
+  </si>
+  <si>
+    <t>Sample Building One</t>
+  </si>
+  <si>
+    <t>Sample City</t>
   </si>
   <si>
     <t>in_progress</t>
   </si>
   <si>
-    <t>Police Station</t>
+    <t>Office</t>
   </si>
   <si>
     <t>MTR-001</t>
   </si>
   <si>
-    <t>SUB-1001</t>
-  </si>
-  <si>
-    <t>ACC-77001</t>
-  </si>
-  <si>
-    <t>Capt. Saad</t>
-  </si>
-  <si>
-    <t>+966 50 111 2222</t>
-  </si>
-  <si>
-    <t>MOI-002</t>
-  </si>
-  <si>
-    <t>Civil Defense — Khamis</t>
-  </si>
-  <si>
-    <t>Khamis Mushait</t>
-  </si>
-  <si>
-    <t>Najd Technical Co.</t>
-  </si>
-  <si>
-    <t>+966 55 222 3333</t>
+    <t>SUB-0001</t>
+  </si>
+  <si>
+    <t>ACC-0001</t>
+  </si>
+  <si>
+    <t>Contact name</t>
+  </si>
+  <si>
+    <t>BLD-002</t>
+  </si>
+  <si>
+    <t>Sample Building Two</t>
   </si>
   <si>
     <t>pending</t>
   </si>
   <si>
-    <t>Civil Defense</t>
+    <t>Warehouse</t>
   </si>
   <si>
     <t>MTR-002</t>
   </si>
   <si>
-    <t>SUB-1002</t>
-  </si>
-  <si>
-    <t>ACC-77002</t>
-  </si>
-  <si>
-    <t>Maj. Nasser</t>
-  </si>
-  <si>
-    <t>+966 55 333 4444</t>
+    <t>SUB-0002</t>
+  </si>
+  <si>
+    <t>ACC-0002</t>
   </si>
   <si>
     <t>esm</t>
@@ -2003,11 +1985,11 @@
       <c r="P2" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="Q2" s="24">
-        <v>18.2164</v>
-      </c>
-      <c r="R2" s="24">
-        <v>42.5053</v>
+      <c r="Q2" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="R2" s="24" t="s">
+        <v>1</v>
       </c>
       <c r="S2" s="23" t="s">
         <v>90</v>
@@ -2826,11 +2808,11 @@
       <c r="D2" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="E2" s="24">
-        <v>18.2164</v>
-      </c>
-      <c r="F2" s="24">
-        <v>42.5053</v>
+      <c r="E2" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>1</v>
       </c>
       <c r="G2" s="23">
         <v>3</v>
@@ -2872,7 +2854,7 @@
         <v>119</v>
       </c>
       <c r="T2" s="23" t="s">
-        <v>120</v>
+        <v>87</v>
       </c>
       <c r="U2" s="23">
         <v>3120</v>
@@ -2883,19 +2865,19 @@
         <v>77</v>
       </c>
       <c r="B3" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="C3" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="23" t="s">
-        <v>122</v>
-      </c>
       <c r="D3" s="23" t="s">
-        <v>123</v>
-      </c>
-      <c r="E3" s="24">
-        <v>18.3</v>
-      </c>
-      <c r="F3" s="24">
-        <v>42.73</v>
+        <v>113</v>
+      </c>
+      <c r="E3" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="24" t="s">
+        <v>1</v>
       </c>
       <c r="G3" s="23">
         <v>2</v>
@@ -2904,13 +2886,13 @@
         <v>2600</v>
       </c>
       <c r="I3" s="23" t="s">
-        <v>124</v>
+        <v>86</v>
       </c>
       <c r="J3" s="23" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="K3" s="23" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="L3" s="23" t="s">
         <v>95</v>
@@ -2922,22 +2904,22 @@
         <v>1</v>
       </c>
       <c r="O3" s="23" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="P3" s="23" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="Q3" s="23" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="R3" s="23" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S3" s="23" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="T3" s="23" t="s">
-        <v>132</v>
+        <v>87</v>
       </c>
       <c r="U3" s="23">
         <v>3120</v>
@@ -3484,22 +3466,22 @@
         <v>97</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -3507,19 +3489,19 @@
         <v>111</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E2" s="23">
         <v>120</v>
       </c>
       <c r="F2" s="23" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="G2" s="23" t="s">
         <v>95</v>
@@ -3530,19 +3512,19 @@
         <v>111</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="E3" s="23">
         <v>15</v>
       </c>
       <c r="F3" s="23" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="G3" s="23" t="s">
         <v>95</v>
@@ -3778,36 +3760,36 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E2" s="23">
         <v>1000</v>
@@ -3818,16 +3800,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E3" s="23">
         <v>200</v>
@@ -4052,31 +4034,31 @@
         <v>97</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="I1" s="16" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="J1" s="16" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -4084,28 +4066,28 @@
         <v>111</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="E2" s="23">
         <v>4</v>
       </c>
       <c r="F2" s="23" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="G2" s="23" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="H2" s="23">
         <v>4</v>
       </c>
       <c r="I2" s="23" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="J2" s="23" t="s">
         <v>95</v>
@@ -4116,28 +4098,28 @@
         <v>111</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="E3" s="23">
         <v>120</v>
       </c>
       <c r="F3" s="23" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="G3" s="23" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="H3" s="23">
         <v>120</v>
       </c>
       <c r="I3" s="23" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="J3" s="23" t="s">
         <v>95</v>
